--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/03. Xác nhận bảo hành/XNBH_AnhTuanBG_120826.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/03. Xác nhận bảo hành/XNBH_AnhTuanBG_120826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 08\03. Xác nhận bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54F544D-BF60-4E92-88E8-87815DECCFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ECD2864-85A2-47F3-AC85-80ACF0D09FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,9 +105,6 @@
     <t>Hướng Xử Lý</t>
   </si>
   <si>
-    <t>Trần Văn Hậu</t>
-  </si>
-  <si>
     <t>Còn BH</t>
   </si>
   <si>
@@ -142,6 +139,9 @@
   </si>
   <si>
     <t>ĐC: A46 TT19 KĐT Văn Quán, Phường Văn Quán, Quận Hà Đông, Hà Nội</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Tùng</t>
   </si>
 </sst>
 </file>
@@ -473,39 +473,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -541,71 +508,104 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -988,236 +988,236 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="7" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16"/>
-      <c r="B1" s="17"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="50" t="s">
+      <c r="A1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="57"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
     </row>
     <row r="2" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="59"/>
+      <c r="A2" s="52"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="59"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="53" t="s">
+      <c r="A4" s="55"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="60"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="45"/>
     </row>
     <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="61"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="48"/>
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="46" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="7" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
       <c r="M8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
       <c r="L9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="18" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="30">
+      <c r="A11" s="19">
         <v>1</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="D11" s="21"/>
+      <c r="E11" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="31" t="s">
+      <c r="H11" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="30" t="s">
+      <c r="I11" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="32" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38" t="s">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
     </row>
     <row r="13" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39" t="s">
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40" t="s">
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="41" t="s">
+      <c r="H13" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="41"/>
+      <c r="I13" s="33"/>
     </row>
     <row r="14" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="48" t="s">
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="49" t="s">
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="48" t="s">
+      <c r="H14" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="48"/>
+      <c r="I14" s="35"/>
     </row>
     <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
@@ -1264,34 +1264,34 @@
       <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
     </row>
     <row r="20" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39" t="s">
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40" t="s">
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="39"/>
+      <c r="H20" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="34"/>
       <c r="J20" s="6"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1308,12 +1308,23 @@
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
     </row>
     <row r="61" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="A13:C13"/>
@@ -1324,17 +1335,6 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="H20:I20"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="1.2" right="1.2" top="1.5" bottom="1.5" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="92" orientation="landscape" r:id="rId1"/>
